--- a/conflict_report.xlsx
+++ b/conflict_report.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="508" uniqueCount="189">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="371" uniqueCount="144">
   <si>
     <t>Message</t>
   </si>
@@ -30,559 +30,424 @@
     <t>Consecutive Slots</t>
   </si>
   <si>
-    <t>Sankhya Gunda</t>
-  </si>
-  <si>
-    <t>Chonticha Phanphanit</t>
-  </si>
-  <si>
-    <t>Erika Lai</t>
-  </si>
-  <si>
-    <t>Adam Vu</t>
+    <t>Nikil Selvam</t>
+  </si>
+  <si>
+    <t>Amanda Ng</t>
+  </si>
+  <si>
+    <t>Jiaying Zhang</t>
+  </si>
+  <si>
+    <t>Sydney Stachovic</t>
+  </si>
+  <si>
+    <t>Jenny Lei</t>
+  </si>
+  <si>
+    <t>Nachiketh Karthik</t>
+  </si>
+  <si>
+    <t>Rachel Ye</t>
+  </si>
+  <si>
+    <t>Max Xing</t>
+  </si>
+  <si>
+    <t>Rhea Rajan</t>
+  </si>
+  <si>
+    <t>Rithika Oumapathy</t>
+  </si>
+  <si>
+    <t>Kristine Ngo</t>
+  </si>
+  <si>
+    <t>Veronica Chang</t>
+  </si>
+  <si>
+    <t>Jingyu Zhang</t>
+  </si>
+  <si>
+    <t>Jenna Nguyen</t>
+  </si>
+  <si>
+    <t>Benson Ngai</t>
+  </si>
+  <si>
+    <t>Helena Xu</t>
+  </si>
+  <si>
+    <t>Jennifer Kim</t>
+  </si>
+  <si>
+    <t>Erin Chang</t>
+  </si>
+  <si>
+    <t>Luke Shen</t>
+  </si>
+  <si>
+    <t>Christine Zhang</t>
+  </si>
+  <si>
+    <t>Emily Chen</t>
+  </si>
+  <si>
+    <t>Jamie Yip</t>
+  </si>
+  <si>
+    <t>Carolyn Suryapermana</t>
+  </si>
+  <si>
+    <t>Sam Lai</t>
+  </si>
+  <si>
+    <t>Alexa Tyberg</t>
+  </si>
+  <si>
+    <t>Gaby Imholte</t>
   </si>
   <si>
     <t>Donnovan Saelee</t>
   </si>
   <si>
-    <t>Maina Berteloot</t>
-  </si>
-  <si>
-    <t>Erin Chang</t>
-  </si>
-  <si>
-    <t>Benson Ngai</t>
-  </si>
-  <si>
-    <t>Minh Nguyen</t>
+    <t>Howell Zhang</t>
+  </si>
+  <si>
+    <t>Leyang Ding</t>
+  </si>
+  <si>
+    <t>Melvin Keat</t>
+  </si>
+  <si>
+    <t>Jerry Qiu</t>
+  </si>
+  <si>
+    <t>Jayden Ma</t>
+  </si>
+  <si>
+    <t>Justin Chen</t>
+  </si>
+  <si>
+    <t>Harry Liu</t>
+  </si>
+  <si>
+    <t>Yuxin Yang</t>
+  </si>
+  <si>
+    <t>Geoffray Lee</t>
+  </si>
+  <si>
+    <t>Hao Yuan Zhu</t>
+  </si>
+  <si>
+    <t>Shakthi Guruswami</t>
+  </si>
+  <si>
+    <t>Nathan Thai</t>
+  </si>
+  <si>
+    <t>Bill Wong</t>
+  </si>
+  <si>
+    <t>Michael Spencer</t>
+  </si>
+  <si>
+    <t>Stanley Hu</t>
+  </si>
+  <si>
+    <t>Kleber Diaz</t>
+  </si>
+  <si>
+    <t>Justin Louie</t>
+  </si>
+  <si>
+    <t>Gaby imholte</t>
+  </si>
+  <si>
+    <t>01:00 - 01:25 → 02:40 - 03:05</t>
+  </si>
+  <si>
+    <t>01:00 - 01:25 → 01:25 - 01:50 → 01:50 - 02:15 → 02:15 - 02:40 → 12:10 - 12:35</t>
+  </si>
+  <si>
+    <t>01:00 - 01:25 → 03:30 - 03:55 → 12:10 - 12:35</t>
+  </si>
+  <si>
+    <t>01:00 - 01:25</t>
+  </si>
+  <si>
+    <t>01:00 - 01:25 → 12:10 - 12:35</t>
+  </si>
+  <si>
+    <t>01:00 - 01:25 → 01:25 - 01:50 → 01:50 - 02:15 → 02:15 - 02:40 → 02:40 - 03:05 → 12:10 - 12:35</t>
+  </si>
+  <si>
+    <t>01:00 - 01:25 → 03:55 - 04:20 → 04:20 - 04:45 → 12:10 - 12:35</t>
+  </si>
+  <si>
+    <t>01:00 - 01:25 → 01:25 - 01:50</t>
+  </si>
+  <si>
+    <t>01:25 - 01:50</t>
+  </si>
+  <si>
+    <t>01:25 - 01:50 → 01:50 - 02:15 → 02:15 - 02:40</t>
+  </si>
+  <si>
+    <t>01:25 - 01:50 → 01:50 - 02:15 → 12:10 - 12:35</t>
+  </si>
+  <si>
+    <t>01:50 - 02:15 → 02:15 - 02:40</t>
+  </si>
+  <si>
+    <t>01:50 - 02:15</t>
+  </si>
+  <si>
+    <t>01:50 - 02:15 → 03:05 - 03:30</t>
+  </si>
+  <si>
+    <t>01:50 - 02:15 → 02:15 - 02:40 → 12:10 - 12:35</t>
+  </si>
+  <si>
+    <t>02:15 - 02:40 → 03:30 - 03:55</t>
+  </si>
+  <si>
+    <t>02:40 - 03:05 → 03:05 - 03:30 → 12:10 - 12:35</t>
+  </si>
+  <si>
+    <t>03:05 - 03:30 → 03:30 - 03:55 → 12:10 - 12:35</t>
+  </si>
+  <si>
+    <t>03:05 - 03:30 → 12:10 - 12:35</t>
+  </si>
+  <si>
+    <t>03:30 - 03:55</t>
+  </si>
+  <si>
+    <t>03:55 - 04:20</t>
+  </si>
+  <si>
+    <t>04:20 - 04:45 → 12:10 - 12:35</t>
+  </si>
+  <si>
+    <t>04:20 - 04:45</t>
+  </si>
+  <si>
+    <t>05:10 - 05:35</t>
+  </si>
+  <si>
+    <t>05:10 - 05:35 → 12:10 - 12:35</t>
+  </si>
+  <si>
+    <t>05:35 - 06:00</t>
+  </si>
+  <si>
+    <t>05:35 - 06:00 → 06:00 - 06:25</t>
+  </si>
+  <si>
+    <t>06:00 - 06:25</t>
+  </si>
+  <si>
+    <t>12:10 - 12:35</t>
+  </si>
+  <si>
+    <t>Total Matches</t>
+  </si>
+  <si>
+    <t>First Slot</t>
+  </si>
+  <si>
+    <t>Last Slot</t>
+  </si>
+  <si>
+    <t>Alex Davis</t>
+  </si>
+  <si>
+    <t>Akhilesh Nidamanuri</t>
+  </si>
+  <si>
+    <t>Jerry Yuan</t>
+  </si>
+  <si>
+    <t>Jason Chen</t>
+  </si>
+  <si>
+    <t>Livia Rice</t>
+  </si>
+  <si>
+    <t>Jon Moser</t>
+  </si>
+  <si>
+    <t>Evan Chen</t>
+  </si>
+  <si>
+    <t>Ryan Lei</t>
+  </si>
+  <si>
+    <t>Sashreek Rewatkar</t>
+  </si>
+  <si>
+    <t>Akshay Ganapathi</t>
+  </si>
+  <si>
+    <t>Sidney Wang</t>
+  </si>
+  <si>
+    <t>Justin Larson</t>
+  </si>
+  <si>
+    <t>Josh Luo</t>
+  </si>
+  <si>
+    <t>Adrian Luo</t>
+  </si>
+  <si>
+    <t>Steffi Ling</t>
+  </si>
+  <si>
+    <t>Winnie Wu</t>
+  </si>
+  <si>
+    <t>Jonathan Li</t>
+  </si>
+  <si>
+    <t>Mariano</t>
+  </si>
+  <si>
+    <t>Emily Lam</t>
+  </si>
+  <si>
+    <t>Suhani</t>
   </si>
   <si>
     <t>Richard Huang</t>
   </si>
   <si>
-    <t>Penny Liu</t>
-  </si>
-  <si>
-    <t>Jenna Nguyen</t>
-  </si>
-  <si>
-    <t>Jenny Lei</t>
+    <t>Leah Diep</t>
+  </si>
+  <si>
+    <t>Adam Dinh</t>
+  </si>
+  <si>
+    <t>Livia RIce</t>
+  </si>
+  <si>
+    <t>Kyle Fang</t>
+  </si>
+  <si>
+    <t>Mariano Elizondo</t>
+  </si>
+  <si>
+    <t>Kyle Kimura</t>
+  </si>
+  <si>
+    <t>Yawei</t>
+  </si>
+  <si>
+    <t>Aaron Lim</t>
+  </si>
+  <si>
+    <t>Aaron Kwan</t>
+  </si>
+  <si>
+    <t>Fahao Mei</t>
+  </si>
+  <si>
+    <t>Sean Tan</t>
+  </si>
+  <si>
+    <t>Samarth</t>
+  </si>
+  <si>
+    <t>Karthik Villavan</t>
+  </si>
+  <si>
+    <t>michael salim</t>
+  </si>
+  <si>
+    <t>Jordan Kwong</t>
+  </si>
+  <si>
+    <t>Junru Su</t>
+  </si>
+  <si>
+    <t>Garrick Chan</t>
+  </si>
+  <si>
+    <t>Chinmay Nallapothula</t>
+  </si>
+  <si>
+    <t>Zenith Ma</t>
+  </si>
+  <si>
+    <t>Taewan Yun</t>
+  </si>
+  <si>
+    <t>Jivan Krisna</t>
+  </si>
+  <si>
+    <t>Marc Ethan Saguiped</t>
+  </si>
+  <si>
+    <t>Nolan Cloud</t>
   </si>
   <si>
     <t>Michael Salim</t>
   </si>
   <si>
-    <t>Benny Wen</t>
-  </si>
-  <si>
-    <t>Nathan Pham</t>
-  </si>
-  <si>
-    <t>Shakthi Guruswami</t>
-  </si>
-  <si>
-    <t>Akhilesh Nidamanuri</t>
-  </si>
-  <si>
-    <t>Tyler Yeh</t>
-  </si>
-  <si>
-    <t>Benjamin Do</t>
-  </si>
-  <si>
-    <t>Genevieve Le</t>
-  </si>
-  <si>
-    <t>Yi Zhong</t>
-  </si>
-  <si>
-    <t>Krishna Gupta</t>
-  </si>
-  <si>
-    <t>Kevin Cuan</t>
-  </si>
-  <si>
-    <t>Suneet Katrekar</t>
-  </si>
-  <si>
-    <t>Sam Lai</t>
-  </si>
-  <si>
-    <t>Sandara Cabagbag</t>
-  </si>
-  <si>
-    <t>Victor Shi</t>
-  </si>
-  <si>
-    <t>Adrian Luu</t>
-  </si>
-  <si>
-    <t>Curtis Luu</t>
-  </si>
-  <si>
-    <t>Bryan Tang</t>
-  </si>
-  <si>
-    <t>Travis Choi</t>
-  </si>
-  <si>
-    <t>Kenneth Darla</t>
-  </si>
-  <si>
-    <t>Ethan Phan</t>
-  </si>
-  <si>
-    <t>Jon Moser</t>
-  </si>
-  <si>
-    <t>Ran Chen</t>
-  </si>
-  <si>
-    <t>Hardy Chen</t>
-  </si>
-  <si>
-    <t>Yuxin Yang</t>
-  </si>
-  <si>
-    <t>Bill Wong</t>
-  </si>
-  <si>
-    <t>Logan Lei Chong</t>
-  </si>
-  <si>
-    <t>Donald Ly</t>
-  </si>
-  <si>
-    <t>Harry Liu</t>
-  </si>
-  <si>
-    <t>Chinmay Nallapothula</t>
-  </si>
-  <si>
-    <t>Nicholas Cen</t>
-  </si>
-  <si>
-    <t>Paul Bishop</t>
-  </si>
-  <si>
-    <t>Sean Hsieh</t>
-  </si>
-  <si>
-    <t>Jordan Kwong</t>
-  </si>
-  <si>
-    <t>Aditya Nagpal</t>
-  </si>
-  <si>
-    <t>Kelvin Chong</t>
-  </si>
-  <si>
-    <t>Brandon Lee</t>
-  </si>
-  <si>
-    <t>Howell Zhang</t>
-  </si>
-  <si>
-    <t>Hao Yuan Zhu</t>
-  </si>
-  <si>
-    <t>Kien Than</t>
-  </si>
-  <si>
-    <t>Jun Quan Yap</t>
-  </si>
-  <si>
-    <t>Xin Huang</t>
-  </si>
-  <si>
-    <t>Rupashi Bahl</t>
-  </si>
-  <si>
-    <t>Rithika Oumapathy</t>
-  </si>
-  <si>
-    <t>Emily Kung</t>
-  </si>
-  <si>
-    <t>Rithwik Vaidun</t>
-  </si>
-  <si>
-    <t>Livia Rice</t>
-  </si>
-  <si>
-    <t>Amber Li</t>
-  </si>
-  <si>
-    <t>Shani Chiu</t>
-  </si>
-  <si>
-    <t>Natalie Luong</t>
-  </si>
-  <si>
-    <t>Ishika Gwalherkar</t>
-  </si>
-  <si>
-    <t>Toan Le</t>
-  </si>
-  <si>
-    <t>Rhea Rajan</t>
-  </si>
-  <si>
-    <t>Justin Larson</t>
-  </si>
-  <si>
-    <t>Jamie Yip</t>
-  </si>
-  <si>
-    <t>Niketana Thimma</t>
-  </si>
-  <si>
-    <t>Jasmeet Dhillon</t>
-  </si>
-  <si>
-    <t>Juan David Liang</t>
-  </si>
-  <si>
-    <t>Chelsea Lin</t>
-  </si>
-  <si>
-    <t>Jennifer Kim</t>
-  </si>
-  <si>
-    <t>01:00 - 01:15 → 01:15 - 01:30 → 10:15 - 10:30 → 10:30 - 10:45 → 10:45 - 11:00 → 11:00 - 11:15 → 11:15 - 11:30 → 11:30 - 11:45</t>
-  </si>
-  <si>
-    <t>01:00 - 01:15</t>
-  </si>
-  <si>
-    <t>01:00 - 01:15 → 11:30 - 11:45</t>
-  </si>
-  <si>
-    <t>01:00 - 01:15 → 01:15 - 01:30 → 02:15 - 02:30</t>
-  </si>
-  <si>
-    <t>01:15 - 01:30</t>
-  </si>
-  <si>
-    <t>01:15 - 01:30 → 10:15 - 10:30 → 11:00 - 11:15 → 11:15 - 11:30 → 11:30 - 11:45</t>
-  </si>
-  <si>
-    <t>01:15 - 01:30 → 01:30 - 01:45 → 01:45 - 02:00 → 02:00 - 02:15</t>
-  </si>
-  <si>
-    <t>01:15 - 01:30 → 11:00 - 11:15 → 11:15 - 11:30</t>
-  </si>
-  <si>
-    <t>01:45 - 02:00</t>
-  </si>
-  <si>
-    <t>01:45 - 02:00 → 11:00 - 11:15</t>
-  </si>
-  <si>
-    <t>02:00 - 02:15</t>
-  </si>
-  <si>
-    <t>02:00 - 02:15 → 10:15 - 10:30 → 10:30 - 10:45 → 10:45 - 11:00 → 11:00 - 11:15</t>
-  </si>
-  <si>
-    <t>02:15 - 02:30</t>
-  </si>
-  <si>
-    <t>02:30 - 02:45</t>
-  </si>
-  <si>
-    <t>02:30 - 02:45 → 02:45 - 03:00 → 03:00 - 03:15</t>
-  </si>
-  <si>
-    <t>02:45 - 03:00 → 03:00 - 03:15</t>
-  </si>
-  <si>
-    <t>02:45 - 03:00 → 03:00 - 03:15 → 03:15 - 03:30</t>
-  </si>
-  <si>
-    <t>03:00 - 03:15 → 03:15 - 03:30 → 10:15 - 10:30</t>
-  </si>
-  <si>
-    <t>03:00 - 03:15 → 04:15 - 04:30 → 10:15 - 10:30</t>
-  </si>
-  <si>
-    <t>03:00 - 03:15</t>
-  </si>
-  <si>
-    <t>03:15 - 03:30</t>
-  </si>
-  <si>
-    <t>03:30 - 03:45</t>
-  </si>
-  <si>
-    <t>04:00 - 04:15</t>
-  </si>
-  <si>
-    <t>04:15 - 04:30</t>
-  </si>
-  <si>
-    <t>04:30 - 04:45</t>
-  </si>
-  <si>
-    <t>04:45 - 05:00</t>
-  </si>
-  <si>
-    <t>05:00 - 05:15</t>
-  </si>
-  <si>
-    <t>10:15 - 10:30 → 10:30 - 10:45</t>
-  </si>
-  <si>
-    <t>10:15 - 10:30 → 10:30 - 10:45 → 10:45 - 11:00 → 11:00 - 11:15 → 11:15 - 11:30 → 11:30 - 11:45</t>
-  </si>
-  <si>
-    <t>10:15 - 10:30 → 10:30 - 10:45 → 10:45 - 11:00 → 11:00 - 11:15 → 11:15 - 11:30</t>
-  </si>
-  <si>
-    <t>10:15 - 10:30 → 11:00 - 11:15</t>
-  </si>
-  <si>
-    <t>10:15 - 10:30</t>
-  </si>
-  <si>
-    <t>10:30 - 10:45</t>
-  </si>
-  <si>
-    <t>10:45 - 11:00 → 11:00 - 11:15</t>
-  </si>
-  <si>
-    <t>10:45 - 11:00</t>
-  </si>
-  <si>
-    <t>10:45 - 11:00 → 11:30 - 11:45</t>
-  </si>
-  <si>
-    <t>11:00 - 11:15</t>
-  </si>
-  <si>
-    <t>11:15 - 11:30</t>
-  </si>
-  <si>
-    <t>11:30 - 11:45</t>
-  </si>
-  <si>
-    <t>Total Matches</t>
-  </si>
-  <si>
-    <t>First Slot</t>
-  </si>
-  <si>
-    <t>Last Slot</t>
-  </si>
-  <si>
-    <t>Sashreek Rewatkar</t>
-  </si>
-  <si>
-    <t>George Wu</t>
-  </si>
-  <si>
-    <t>Emily Lam</t>
-  </si>
-  <si>
-    <t>Sydney Stachovic</t>
-  </si>
-  <si>
-    <t>Khoa Nguyen</t>
-  </si>
-  <si>
-    <t>Leyang Ding</t>
-  </si>
-  <si>
-    <t>Seong Kang Kwong</t>
-  </si>
-  <si>
-    <t>Alex Nguyen</t>
-  </si>
-  <si>
-    <t>Jolene Wei</t>
-  </si>
-  <si>
-    <t>Jiaying Zhang</t>
-  </si>
-  <si>
-    <t>Sam Sridhara</t>
-  </si>
-  <si>
-    <t>Iris Lee</t>
-  </si>
-  <si>
-    <t>Alex Luong</t>
-  </si>
-  <si>
-    <t>Akshay Ganapathi</t>
-  </si>
-  <si>
-    <t>Maharshi Mandapati</t>
-  </si>
-  <si>
-    <t>Khang Nguyen</t>
-  </si>
-  <si>
-    <t>Marc Ethan Saguiped</t>
-  </si>
-  <si>
-    <t>Kyle Wong</t>
-  </si>
-  <si>
-    <t>Justin Louie</t>
-  </si>
-  <si>
-    <t>Adam Dinh</t>
-  </si>
-  <si>
-    <t>Vivian Wang</t>
-  </si>
-  <si>
-    <t>Jayden Ma</t>
-  </si>
-  <si>
-    <t>Kyle Kimura</t>
-  </si>
-  <si>
-    <t>Jasmin Chan</t>
-  </si>
-  <si>
-    <t>Giang Phi</t>
-  </si>
-  <si>
-    <t>Fiona Chen</t>
-  </si>
-  <si>
-    <t>Isaac Li</t>
-  </si>
-  <si>
-    <t>Sidney Wang</t>
-  </si>
-  <si>
-    <t>Carolyn</t>
-  </si>
-  <si>
-    <t>Parth Gopakumar</t>
-  </si>
-  <si>
-    <t>Garrick Chan</t>
-  </si>
-  <si>
-    <t>Junru Su</t>
-  </si>
-  <si>
-    <t>Victor Tran</t>
-  </si>
-  <si>
-    <t>Cheng Huan Yu</t>
-  </si>
-  <si>
-    <t>Mervyn Neo</t>
-  </si>
-  <si>
-    <t>Khoa Tran</t>
-  </si>
-  <si>
-    <t>Stanley Hu</t>
-  </si>
-  <si>
-    <t>Shyam Sundararajan</t>
-  </si>
-  <si>
-    <t>Ryan Lei</t>
-  </si>
-  <si>
-    <t>Taewan Yun</t>
-  </si>
-  <si>
-    <t>Geoffray Lee</t>
-  </si>
-  <si>
-    <t>Chenyi Zhang</t>
-  </si>
-  <si>
-    <t>Kai Wagner</t>
-  </si>
-  <si>
-    <t>Aaron Lim</t>
-  </si>
-  <si>
-    <t>Adrian Luo</t>
+    <t>Jivan Krishna</t>
   </si>
   <si>
     <t>01:00</t>
   </si>
   <si>
-    <t>01:30</t>
-  </si>
-  <si>
-    <t>01:15</t>
+    <t>01:50</t>
+  </si>
+  <si>
+    <t>01:25</t>
+  </si>
+  <si>
+    <t>03:05</t>
+  </si>
+  <si>
+    <t>02:40</t>
   </si>
   <si>
     <t>02:15</t>
   </si>
   <si>
-    <t>01:45</t>
-  </si>
-  <si>
-    <t>03:00</t>
-  </si>
-  <si>
-    <t>10:15</t>
-  </si>
-  <si>
-    <t>02:30</t>
-  </si>
-  <si>
-    <t>02:00</t>
-  </si>
-  <si>
-    <t>03:45</t>
-  </si>
-  <si>
-    <t>02:45</t>
+    <t>03:55</t>
+  </si>
+  <si>
+    <t>05:10</t>
+  </si>
+  <si>
+    <t>05:35</t>
   </si>
   <si>
     <t>03:30</t>
   </si>
   <si>
-    <t>03:15</t>
-  </si>
-  <si>
-    <t>11:00</t>
-  </si>
-  <si>
-    <t>04:00</t>
-  </si>
-  <si>
-    <t>04:15</t>
-  </si>
-  <si>
-    <t>04:30</t>
-  </si>
-  <si>
     <t>04:45</t>
   </si>
   <si>
-    <t>05:00</t>
-  </si>
-  <si>
-    <t>11:45</t>
-  </si>
-  <si>
-    <t>11:15</t>
-  </si>
-  <si>
-    <t>11:30</t>
-  </si>
-  <si>
-    <t>10:30</t>
-  </si>
-  <si>
-    <t>10:45</t>
-  </si>
-  <si>
-    <t>05:15</t>
+    <t>06:00</t>
+  </si>
+  <si>
+    <t>06:25</t>
+  </si>
+  <si>
+    <t>06:50</t>
+  </si>
+  <si>
+    <t>12:35</t>
+  </si>
+  <si>
+    <t>12:10</t>
+  </si>
+  <si>
+    <t>04:20</t>
   </si>
 </sst>
 </file>
@@ -960,7 +825,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B74"/>
+  <dimension ref="A1:B46"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -976,7 +841,7 @@
         <v>4</v>
       </c>
       <c r="B2" t="s">
-        <v>77</v>
+        <v>49</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -984,7 +849,7 @@
         <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>78</v>
+        <v>50</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -992,7 +857,7 @@
         <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>79</v>
+        <v>50</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -1000,7 +865,7 @@
         <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>78</v>
+        <v>51</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -1008,7 +873,7 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>78</v>
+        <v>52</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -1016,7 +881,7 @@
         <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>80</v>
+        <v>53</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -1024,7 +889,7 @@
         <v>10</v>
       </c>
       <c r="B8" t="s">
-        <v>78</v>
+        <v>54</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -1032,7 +897,7 @@
         <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>81</v>
+        <v>55</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -1040,7 +905,7 @@
         <v>12</v>
       </c>
       <c r="B10" t="s">
-        <v>82</v>
+        <v>56</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -1048,7 +913,7 @@
         <v>13</v>
       </c>
       <c r="B11" t="s">
-        <v>81</v>
+        <v>57</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -1056,7 +921,7 @@
         <v>14</v>
       </c>
       <c r="B12" t="s">
-        <v>81</v>
+        <v>58</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -1064,7 +929,7 @@
         <v>15</v>
       </c>
       <c r="B13" t="s">
-        <v>83</v>
+        <v>59</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -1072,7 +937,7 @@
         <v>16</v>
       </c>
       <c r="B14" t="s">
-        <v>84</v>
+        <v>59</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -1080,7 +945,7 @@
         <v>17</v>
       </c>
       <c r="B15" t="s">
-        <v>85</v>
+        <v>57</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -1088,7 +953,7 @@
         <v>18</v>
       </c>
       <c r="B16" t="s">
-        <v>85</v>
+        <v>60</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -1096,7 +961,7 @@
         <v>19</v>
       </c>
       <c r="B17" t="s">
-        <v>85</v>
+        <v>60</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -1104,7 +969,7 @@
         <v>20</v>
       </c>
       <c r="B18" t="s">
-        <v>86</v>
+        <v>61</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -1112,7 +977,7 @@
         <v>21</v>
       </c>
       <c r="B19" t="s">
-        <v>85</v>
+        <v>62</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -1120,7 +985,7 @@
         <v>22</v>
       </c>
       <c r="B20" t="s">
-        <v>87</v>
+        <v>61</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -1128,7 +993,7 @@
         <v>23</v>
       </c>
       <c r="B21" t="s">
-        <v>88</v>
+        <v>63</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -1136,7 +1001,7 @@
         <v>24</v>
       </c>
       <c r="B22" t="s">
-        <v>87</v>
+        <v>64</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -1144,7 +1009,7 @@
         <v>25</v>
       </c>
       <c r="B23" t="s">
-        <v>89</v>
+        <v>65</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -1152,7 +1017,7 @@
         <v>26</v>
       </c>
       <c r="B24" t="s">
-        <v>90</v>
+        <v>65</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -1160,7 +1025,7 @@
         <v>27</v>
       </c>
       <c r="B25" t="s">
-        <v>90</v>
+        <v>66</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -1168,7 +1033,7 @@
         <v>28</v>
       </c>
       <c r="B26" t="s">
-        <v>90</v>
+        <v>67</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -1176,7 +1041,7 @@
         <v>29</v>
       </c>
       <c r="B27" t="s">
-        <v>90</v>
+        <v>68</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -1184,7 +1049,7 @@
         <v>30</v>
       </c>
       <c r="B28" t="s">
-        <v>91</v>
+        <v>68</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -1192,7 +1057,7 @@
         <v>31</v>
       </c>
       <c r="B29" t="s">
-        <v>92</v>
+        <v>68</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -1200,7 +1065,7 @@
         <v>32</v>
       </c>
       <c r="B30" t="s">
-        <v>93</v>
+        <v>69</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -1208,7 +1073,7 @@
         <v>33</v>
       </c>
       <c r="B31" t="s">
-        <v>92</v>
+        <v>70</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -1216,7 +1081,7 @@
         <v>34</v>
       </c>
       <c r="B32" t="s">
-        <v>94</v>
+        <v>71</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -1224,7 +1089,7 @@
         <v>35</v>
       </c>
       <c r="B33" t="s">
-        <v>95</v>
+        <v>71</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -1232,7 +1097,7 @@
         <v>36</v>
       </c>
       <c r="B34" t="s">
-        <v>96</v>
+        <v>71</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -1240,7 +1105,7 @@
         <v>37</v>
       </c>
       <c r="B35" t="s">
-        <v>96</v>
+        <v>71</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -1248,7 +1113,7 @@
         <v>38</v>
       </c>
       <c r="B36" t="s">
-        <v>97</v>
+        <v>72</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -1256,7 +1121,7 @@
         <v>39</v>
       </c>
       <c r="B37" t="s">
-        <v>97</v>
+        <v>72</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -1264,7 +1129,7 @@
         <v>40</v>
       </c>
       <c r="B38" t="s">
-        <v>98</v>
+        <v>73</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -1272,7 +1137,7 @@
         <v>41</v>
       </c>
       <c r="B39" t="s">
-        <v>98</v>
+        <v>74</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -1280,7 +1145,7 @@
         <v>42</v>
       </c>
       <c r="B40" t="s">
-        <v>98</v>
+        <v>75</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -1288,7 +1153,7 @@
         <v>43</v>
       </c>
       <c r="B41" t="s">
-        <v>98</v>
+        <v>76</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -1296,7 +1161,7 @@
         <v>44</v>
       </c>
       <c r="B42" t="s">
-        <v>98</v>
+        <v>76</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -1304,7 +1169,7 @@
         <v>45</v>
       </c>
       <c r="B43" t="s">
-        <v>99</v>
+        <v>76</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -1312,7 +1177,7 @@
         <v>46</v>
       </c>
       <c r="B44" t="s">
-        <v>100</v>
+        <v>76</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -1320,7 +1185,7 @@
         <v>47</v>
       </c>
       <c r="B45" t="s">
-        <v>100</v>
+        <v>76</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -1328,231 +1193,7 @@
         <v>48</v>
       </c>
       <c r="B46" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2">
-      <c r="A47" t="s">
-        <v>49</v>
-      </c>
-      <c r="B47" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2">
-      <c r="A48" t="s">
-        <v>50</v>
-      </c>
-      <c r="B48" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2">
-      <c r="A49" t="s">
-        <v>51</v>
-      </c>
-      <c r="B49" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2">
-      <c r="A50" t="s">
-        <v>52</v>
-      </c>
-      <c r="B50" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2">
-      <c r="A51" t="s">
-        <v>53</v>
-      </c>
-      <c r="B51" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2">
-      <c r="A52" t="s">
-        <v>54</v>
-      </c>
-      <c r="B52" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2">
-      <c r="A53" t="s">
-        <v>55</v>
-      </c>
-      <c r="B53" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="54" spans="1:2">
-      <c r="A54" t="s">
-        <v>56</v>
-      </c>
-      <c r="B54" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="55" spans="1:2">
-      <c r="A55" t="s">
-        <v>57</v>
-      </c>
-      <c r="B55" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="56" spans="1:2">
-      <c r="A56" t="s">
-        <v>58</v>
-      </c>
-      <c r="B56" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="57" spans="1:2">
-      <c r="A57" t="s">
-        <v>59</v>
-      </c>
-      <c r="B57" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="58" spans="1:2">
-      <c r="A58" t="s">
-        <v>60</v>
-      </c>
-      <c r="B58" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="59" spans="1:2">
-      <c r="A59" t="s">
-        <v>61</v>
-      </c>
-      <c r="B59" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="60" spans="1:2">
-      <c r="A60" t="s">
-        <v>62</v>
-      </c>
-      <c r="B60" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="61" spans="1:2">
-      <c r="A61" t="s">
-        <v>63</v>
-      </c>
-      <c r="B61" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="62" spans="1:2">
-      <c r="A62" t="s">
-        <v>64</v>
-      </c>
-      <c r="B62" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="63" spans="1:2">
-      <c r="A63" t="s">
-        <v>65</v>
-      </c>
-      <c r="B63" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="64" spans="1:2">
-      <c r="A64" t="s">
-        <v>66</v>
-      </c>
-      <c r="B64" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="65" spans="1:2">
-      <c r="A65" t="s">
-        <v>67</v>
-      </c>
-      <c r="B65" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="66" spans="1:2">
-      <c r="A66" t="s">
-        <v>68</v>
-      </c>
-      <c r="B66" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="67" spans="1:2">
-      <c r="A67" t="s">
-        <v>69</v>
-      </c>
-      <c r="B67" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="68" spans="1:2">
-      <c r="A68" t="s">
-        <v>70</v>
-      </c>
-      <c r="B68" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="69" spans="1:2">
-      <c r="A69" t="s">
-        <v>71</v>
-      </c>
-      <c r="B69" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="70" spans="1:2">
-      <c r="A70" t="s">
-        <v>72</v>
-      </c>
-      <c r="B70" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="71" spans="1:2">
-      <c r="A71" t="s">
-        <v>73</v>
-      </c>
-      <c r="B71" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="72" spans="1:2">
-      <c r="A72" t="s">
-        <v>74</v>
-      </c>
-      <c r="B72" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="73" spans="1:2">
-      <c r="A73" t="s">
-        <v>75</v>
-      </c>
-      <c r="B73" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="74" spans="1:2">
-      <c r="A74" t="s">
-        <v>76</v>
-      </c>
-      <c r="B74" t="s">
-        <v>115</v>
+        <v>77</v>
       </c>
     </row>
   </sheetData>
@@ -1562,7 +1203,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D119"/>
+  <dimension ref="A1:D92"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -1570,1665 +1211,1287 @@
         <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>116</v>
+        <v>78</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>117</v>
+        <v>79</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>118</v>
+        <v>80</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B2">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C2" t="s">
-        <v>164</v>
+        <v>127</v>
       </c>
       <c r="D2" t="s">
-        <v>183</v>
+        <v>141</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" t="s">
-        <v>63</v>
+        <v>6</v>
       </c>
       <c r="B3">
         <v>8</v>
       </c>
       <c r="C3" t="s">
-        <v>165</v>
+        <v>127</v>
       </c>
       <c r="D3" t="s">
-        <v>183</v>
+        <v>141</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B4">
         <v>8</v>
       </c>
       <c r="C4" t="s">
-        <v>166</v>
+        <v>127</v>
       </c>
       <c r="D4" t="s">
-        <v>183</v>
+        <v>141</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" t="s">
-        <v>66</v>
+        <v>11</v>
       </c>
       <c r="B5">
         <v>8</v>
       </c>
       <c r="C5" t="s">
-        <v>167</v>
+        <v>127</v>
       </c>
       <c r="D5" t="s">
-        <v>183</v>
+        <v>141</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" t="s">
-        <v>73</v>
+        <v>8</v>
       </c>
       <c r="B6">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C6" t="s">
-        <v>164</v>
+        <v>127</v>
       </c>
       <c r="D6" t="s">
-        <v>183</v>
+        <v>142</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" t="s">
-        <v>59</v>
+        <v>7</v>
       </c>
       <c r="B7">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C7" t="s">
-        <v>165</v>
+        <v>127</v>
       </c>
       <c r="D7" t="s">
-        <v>183</v>
+        <v>141</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" t="s">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="B8">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C8" t="s">
-        <v>164</v>
+        <v>127</v>
       </c>
       <c r="D8" t="s">
-        <v>184</v>
+        <v>141</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" t="s">
-        <v>67</v>
+        <v>19</v>
       </c>
       <c r="B9">
         <v>6</v>
       </c>
       <c r="C9" t="s">
-        <v>164</v>
+        <v>127</v>
       </c>
       <c r="D9" t="s">
-        <v>185</v>
+        <v>142</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" t="s">
-        <v>60</v>
+        <v>21</v>
       </c>
       <c r="B10">
         <v>6</v>
       </c>
       <c r="C10" t="s">
-        <v>166</v>
+        <v>128</v>
       </c>
       <c r="D10" t="s">
-        <v>184</v>
+        <v>142</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" t="s">
-        <v>64</v>
+        <v>9</v>
       </c>
       <c r="B11">
         <v>6</v>
       </c>
       <c r="C11" t="s">
-        <v>167</v>
+        <v>127</v>
       </c>
       <c r="D11" t="s">
-        <v>183</v>
+        <v>141</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="B12">
         <v>6</v>
       </c>
       <c r="C12" t="s">
-        <v>168</v>
+        <v>127</v>
       </c>
       <c r="D12" t="s">
-        <v>183</v>
+        <v>141</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" t="s">
-        <v>62</v>
+        <v>4</v>
       </c>
       <c r="B13">
         <v>6</v>
       </c>
       <c r="C13" t="s">
-        <v>164</v>
+        <v>127</v>
       </c>
       <c r="D13" t="s">
-        <v>184</v>
+        <v>142</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="B14">
         <v>6</v>
       </c>
       <c r="C14" t="s">
-        <v>169</v>
+        <v>129</v>
       </c>
       <c r="D14" t="s">
-        <v>186</v>
+        <v>141</v>
       </c>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" t="s">
-        <v>61</v>
+        <v>15</v>
       </c>
       <c r="B15">
         <v>6</v>
       </c>
       <c r="C15" t="s">
-        <v>170</v>
+        <v>129</v>
       </c>
       <c r="D15" t="s">
-        <v>185</v>
+        <v>141</v>
       </c>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" t="s">
-        <v>119</v>
+        <v>16</v>
       </c>
       <c r="B16">
         <v>6</v>
       </c>
       <c r="C16" t="s">
-        <v>164</v>
+        <v>129</v>
       </c>
       <c r="D16" t="s">
-        <v>184</v>
+        <v>141</v>
       </c>
     </row>
     <row r="17" spans="1:4">
       <c r="A17" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B17">
         <v>6</v>
       </c>
       <c r="C17" t="s">
-        <v>169</v>
+        <v>127</v>
       </c>
       <c r="D17" t="s">
-        <v>186</v>
+        <v>141</v>
       </c>
     </row>
     <row r="18" spans="1:4">
       <c r="A18" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="B18">
         <v>6</v>
       </c>
       <c r="C18" t="s">
-        <v>166</v>
+        <v>127</v>
       </c>
       <c r="D18" t="s">
-        <v>187</v>
+        <v>141</v>
       </c>
     </row>
     <row r="19" spans="1:4">
       <c r="A19" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B19">
         <v>6</v>
       </c>
       <c r="C19" t="s">
-        <v>171</v>
+        <v>130</v>
       </c>
       <c r="D19" t="s">
-        <v>183</v>
+        <v>141</v>
       </c>
     </row>
     <row r="20" spans="1:4">
       <c r="A20" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="B20">
         <v>6</v>
       </c>
       <c r="C20" t="s">
-        <v>164</v>
+        <v>128</v>
       </c>
       <c r="D20" t="s">
-        <v>183</v>
+        <v>141</v>
       </c>
     </row>
     <row r="21" spans="1:4">
       <c r="A21" t="s">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="B21">
         <v>6</v>
       </c>
       <c r="C21" t="s">
-        <v>166</v>
+        <v>127</v>
       </c>
       <c r="D21" t="s">
-        <v>186</v>
+        <v>141</v>
       </c>
     </row>
     <row r="22" spans="1:4">
       <c r="A22" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="B22">
         <v>6</v>
       </c>
       <c r="C22" t="s">
-        <v>166</v>
+        <v>127</v>
       </c>
       <c r="D22" t="s">
-        <v>185</v>
+        <v>141</v>
       </c>
     </row>
     <row r="23" spans="1:4">
       <c r="A23" t="s">
-        <v>68</v>
+        <v>31</v>
       </c>
       <c r="B23">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C23" t="s">
-        <v>168</v>
+        <v>127</v>
       </c>
       <c r="D23" t="s">
-        <v>187</v>
+        <v>141</v>
       </c>
     </row>
     <row r="24" spans="1:4">
       <c r="A24" t="s">
-        <v>32</v>
+        <v>81</v>
       </c>
       <c r="B24">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C24" t="s">
-        <v>164</v>
+        <v>127</v>
       </c>
       <c r="D24" t="s">
-        <v>175</v>
+        <v>142</v>
       </c>
     </row>
     <row r="25" spans="1:4">
       <c r="A25" t="s">
-        <v>9</v>
+        <v>35</v>
       </c>
       <c r="B25">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C25" t="s">
-        <v>164</v>
+        <v>127</v>
       </c>
       <c r="D25" t="s">
-        <v>183</v>
+        <v>141</v>
       </c>
     </row>
     <row r="26" spans="1:4">
       <c r="A26" t="s">
-        <v>72</v>
+        <v>48</v>
       </c>
       <c r="B26">
         <v>4</v>
       </c>
       <c r="C26" t="s">
-        <v>165</v>
+        <v>131</v>
       </c>
       <c r="D26" t="s">
-        <v>177</v>
+        <v>141</v>
       </c>
     </row>
     <row r="27" spans="1:4">
       <c r="A27" t="s">
-        <v>14</v>
+        <v>82</v>
       </c>
       <c r="B27">
         <v>4</v>
       </c>
       <c r="C27" t="s">
-        <v>166</v>
+        <v>127</v>
       </c>
       <c r="D27" t="s">
-        <v>170</v>
+        <v>141</v>
       </c>
     </row>
     <row r="28" spans="1:4">
       <c r="A28" t="s">
-        <v>71</v>
+        <v>83</v>
       </c>
       <c r="B28">
         <v>4</v>
       </c>
       <c r="C28" t="s">
-        <v>164</v>
+        <v>127</v>
       </c>
       <c r="D28" t="s">
-        <v>177</v>
+        <v>142</v>
       </c>
     </row>
     <row r="29" spans="1:4">
       <c r="A29" t="s">
-        <v>58</v>
+        <v>32</v>
       </c>
       <c r="B29">
         <v>4</v>
       </c>
       <c r="C29" t="s">
-        <v>172</v>
+        <v>130</v>
       </c>
       <c r="D29" t="s">
-        <v>187</v>
+        <v>134</v>
       </c>
     </row>
     <row r="30" spans="1:4">
       <c r="A30" t="s">
-        <v>120</v>
+        <v>14</v>
       </c>
       <c r="B30">
         <v>4</v>
       </c>
       <c r="C30" t="s">
-        <v>166</v>
+        <v>129</v>
       </c>
       <c r="D30" t="s">
-        <v>170</v>
+        <v>131</v>
       </c>
     </row>
     <row r="31" spans="1:4">
       <c r="A31" t="s">
-        <v>65</v>
+        <v>84</v>
       </c>
       <c r="B31">
         <v>4</v>
       </c>
       <c r="C31" t="s">
-        <v>166</v>
+        <v>130</v>
       </c>
       <c r="D31" t="s">
-        <v>177</v>
+        <v>141</v>
       </c>
     </row>
     <row r="32" spans="1:4">
       <c r="A32" t="s">
-        <v>21</v>
+        <v>85</v>
       </c>
       <c r="B32">
         <v>4</v>
       </c>
       <c r="C32" t="s">
-        <v>168</v>
+        <v>127</v>
       </c>
       <c r="D32" t="s">
-        <v>186</v>
+        <v>141</v>
       </c>
     </row>
     <row r="33" spans="1:4">
       <c r="A33" t="s">
-        <v>121</v>
+        <v>17</v>
       </c>
       <c r="B33">
         <v>4</v>
       </c>
       <c r="C33" t="s">
-        <v>172</v>
+        <v>129</v>
       </c>
       <c r="D33" t="s">
-        <v>185</v>
+        <v>141</v>
       </c>
     </row>
     <row r="34" spans="1:4">
       <c r="A34" t="s">
-        <v>69</v>
+        <v>86</v>
       </c>
       <c r="B34">
         <v>4</v>
       </c>
       <c r="C34" t="s">
-        <v>164</v>
+        <v>129</v>
       </c>
       <c r="D34" t="s">
-        <v>187</v>
+        <v>135</v>
       </c>
     </row>
     <row r="35" spans="1:4">
       <c r="A35" t="s">
-        <v>122</v>
+        <v>36</v>
       </c>
       <c r="B35">
         <v>4</v>
       </c>
       <c r="C35" t="s">
-        <v>172</v>
+        <v>129</v>
       </c>
       <c r="D35" t="s">
-        <v>183</v>
+        <v>135</v>
       </c>
     </row>
     <row r="36" spans="1:4">
       <c r="A36" t="s">
-        <v>70</v>
+        <v>34</v>
       </c>
       <c r="B36">
         <v>4</v>
       </c>
       <c r="C36" t="s">
-        <v>168</v>
+        <v>129</v>
       </c>
       <c r="D36" t="s">
-        <v>184</v>
+        <v>137</v>
       </c>
     </row>
     <row r="37" spans="1:4">
       <c r="A37" t="s">
-        <v>123</v>
+        <v>87</v>
       </c>
       <c r="B37">
         <v>4</v>
       </c>
       <c r="C37" t="s">
-        <v>173</v>
+        <v>129</v>
       </c>
       <c r="D37" t="s">
-        <v>185</v>
+        <v>133</v>
       </c>
     </row>
     <row r="38" spans="1:4">
       <c r="A38" t="s">
-        <v>74</v>
+        <v>41</v>
       </c>
       <c r="B38">
         <v>4</v>
       </c>
       <c r="C38" t="s">
-        <v>172</v>
+        <v>132</v>
       </c>
       <c r="D38" t="s">
-        <v>184</v>
+        <v>138</v>
       </c>
     </row>
     <row r="39" spans="1:4">
       <c r="A39" t="s">
-        <v>10</v>
+        <v>37</v>
       </c>
       <c r="B39">
         <v>4</v>
       </c>
       <c r="C39" t="s">
-        <v>164</v>
+        <v>129</v>
       </c>
       <c r="D39" t="s">
-        <v>186</v>
+        <v>135</v>
       </c>
     </row>
     <row r="40" spans="1:4">
       <c r="A40" t="s">
-        <v>11</v>
+        <v>39</v>
       </c>
       <c r="B40">
         <v>4</v>
       </c>
       <c r="C40" t="s">
-        <v>166</v>
+        <v>132</v>
       </c>
       <c r="D40" t="s">
-        <v>187</v>
+        <v>135</v>
       </c>
     </row>
     <row r="41" spans="1:4">
       <c r="A41" t="s">
-        <v>124</v>
+        <v>24</v>
       </c>
       <c r="B41">
         <v>4</v>
       </c>
       <c r="C41" t="s">
-        <v>172</v>
+        <v>132</v>
       </c>
       <c r="D41" t="s">
-        <v>187</v>
+        <v>133</v>
       </c>
     </row>
     <row r="42" spans="1:4">
       <c r="A42" t="s">
-        <v>125</v>
+        <v>18</v>
       </c>
       <c r="B42">
         <v>4</v>
       </c>
       <c r="C42" t="s">
-        <v>171</v>
+        <v>128</v>
       </c>
       <c r="D42" t="s">
-        <v>183</v>
+        <v>137</v>
       </c>
     </row>
     <row r="43" spans="1:4">
       <c r="A43" t="s">
-        <v>126</v>
+        <v>20</v>
       </c>
       <c r="B43">
         <v>4</v>
       </c>
       <c r="C43" t="s">
-        <v>164</v>
+        <v>128</v>
       </c>
       <c r="D43" t="s">
-        <v>185</v>
+        <v>137</v>
       </c>
     </row>
     <row r="44" spans="1:4">
       <c r="A44" t="s">
-        <v>24</v>
+        <v>88</v>
       </c>
       <c r="B44">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C44" t="s">
-        <v>165</v>
+        <v>127</v>
       </c>
       <c r="D44" t="s">
-        <v>177</v>
+        <v>142</v>
       </c>
     </row>
     <row r="45" spans="1:4">
       <c r="A45" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="B45">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C45" t="s">
-        <v>166</v>
+        <v>133</v>
       </c>
       <c r="D45" t="s">
-        <v>183</v>
+        <v>142</v>
       </c>
     </row>
     <row r="46" spans="1:4">
       <c r="A46" t="s">
+        <v>90</v>
+      </c>
+      <c r="B46">
+        <v>3</v>
+      </c>
+      <c r="C46" t="s">
         <v>127</v>
       </c>
-      <c r="B46">
-        <v>4</v>
-      </c>
-      <c r="C46" t="s">
-        <v>174</v>
-      </c>
       <c r="D46" t="s">
-        <v>183</v>
+        <v>138</v>
       </c>
     </row>
     <row r="47" spans="1:4">
       <c r="A47" t="s">
-        <v>41</v>
+        <v>91</v>
       </c>
       <c r="B47">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C47" t="s">
-        <v>175</v>
+        <v>129</v>
       </c>
       <c r="D47" t="s">
-        <v>185</v>
+        <v>135</v>
       </c>
     </row>
     <row r="48" spans="1:4">
       <c r="A48" t="s">
-        <v>25</v>
+        <v>92</v>
       </c>
       <c r="B48">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C48" t="s">
-        <v>164</v>
+        <v>127</v>
       </c>
       <c r="D48" t="s">
-        <v>184</v>
+        <v>138</v>
       </c>
     </row>
     <row r="49" spans="1:4">
       <c r="A49" t="s">
-        <v>7</v>
+        <v>93</v>
       </c>
       <c r="B49">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C49" t="s">
-        <v>164</v>
+        <v>132</v>
       </c>
       <c r="D49" t="s">
-        <v>183</v>
+        <v>134</v>
       </c>
     </row>
     <row r="50" spans="1:4">
       <c r="A50" t="s">
-        <v>75</v>
+        <v>44</v>
       </c>
       <c r="B50">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C50" t="s">
-        <v>172</v>
+        <v>134</v>
       </c>
       <c r="D50" t="s">
-        <v>185</v>
+        <v>139</v>
       </c>
     </row>
     <row r="51" spans="1:4">
       <c r="A51" t="s">
-        <v>128</v>
+        <v>38</v>
       </c>
       <c r="B51">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C51" t="s">
-        <v>164</v>
+        <v>134</v>
       </c>
       <c r="D51" t="s">
-        <v>184</v>
+        <v>139</v>
       </c>
     </row>
     <row r="52" spans="1:4">
       <c r="A52" t="s">
-        <v>129</v>
+        <v>94</v>
       </c>
       <c r="B52">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C52" t="s">
-        <v>168</v>
+        <v>133</v>
       </c>
       <c r="D52" t="s">
-        <v>184</v>
+        <v>138</v>
       </c>
     </row>
     <row r="53" spans="1:4">
       <c r="A53" t="s">
-        <v>13</v>
+        <v>46</v>
       </c>
       <c r="B53">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C53" t="s">
-        <v>166</v>
+        <v>134</v>
       </c>
       <c r="D53" t="s">
-        <v>185</v>
+        <v>139</v>
       </c>
     </row>
     <row r="54" spans="1:4">
       <c r="A54" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="B54">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C54" t="s">
-        <v>171</v>
+        <v>135</v>
       </c>
       <c r="D54" t="s">
-        <v>185</v>
+        <v>139</v>
       </c>
     </row>
     <row r="55" spans="1:4">
       <c r="A55" t="s">
-        <v>130</v>
+        <v>95</v>
       </c>
       <c r="B55">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C55" t="s">
-        <v>164</v>
+        <v>131</v>
       </c>
       <c r="D55" t="s">
-        <v>185</v>
+        <v>137</v>
       </c>
     </row>
     <row r="56" spans="1:4">
       <c r="A56" t="s">
-        <v>29</v>
+        <v>96</v>
       </c>
       <c r="B56">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C56" t="s">
-        <v>171</v>
+        <v>132</v>
       </c>
       <c r="D56" t="s">
-        <v>180</v>
+        <v>133</v>
       </c>
     </row>
     <row r="57" spans="1:4">
       <c r="A57" t="s">
-        <v>43</v>
+        <v>97</v>
       </c>
       <c r="B57">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C57" t="s">
-        <v>171</v>
+        <v>128</v>
       </c>
       <c r="D57" t="s">
-        <v>179</v>
+        <v>137</v>
       </c>
     </row>
     <row r="58" spans="1:4">
       <c r="A58" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="B58">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C58" t="s">
-        <v>164</v>
+        <v>129</v>
       </c>
       <c r="D58" t="s">
-        <v>173</v>
+        <v>128</v>
       </c>
     </row>
     <row r="59" spans="1:4">
       <c r="A59" t="s">
-        <v>18</v>
+        <v>98</v>
       </c>
       <c r="B59">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C59" t="s">
-        <v>168</v>
+        <v>129</v>
       </c>
       <c r="D59" t="s">
-        <v>185</v>
+        <v>143</v>
       </c>
     </row>
     <row r="60" spans="1:4">
       <c r="A60" t="s">
-        <v>131</v>
+        <v>99</v>
       </c>
       <c r="B60">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C60" t="s">
-        <v>164</v>
+        <v>128</v>
       </c>
       <c r="D60" t="s">
-        <v>181</v>
+        <v>130</v>
       </c>
     </row>
     <row r="61" spans="1:4">
       <c r="A61" t="s">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="B61">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C61" t="s">
-        <v>164</v>
+        <v>136</v>
       </c>
       <c r="D61" t="s">
-        <v>175</v>
+        <v>133</v>
       </c>
     </row>
     <row r="62" spans="1:4">
       <c r="A62" t="s">
-        <v>45</v>
+        <v>100</v>
       </c>
       <c r="B62">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C62" t="s">
-        <v>166</v>
+        <v>130</v>
       </c>
       <c r="D62" t="s">
-        <v>179</v>
+        <v>137</v>
       </c>
     </row>
     <row r="63" spans="1:4">
       <c r="A63" t="s">
-        <v>132</v>
+        <v>101</v>
       </c>
       <c r="B63">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C63" t="s">
-        <v>166</v>
+        <v>130</v>
       </c>
       <c r="D63" t="s">
-        <v>178</v>
+        <v>133</v>
       </c>
     </row>
     <row r="64" spans="1:4">
       <c r="A64" t="s">
-        <v>49</v>
+        <v>102</v>
       </c>
       <c r="B64">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C64" t="s">
-        <v>168</v>
+        <v>131</v>
       </c>
       <c r="D64" t="s">
-        <v>180</v>
+        <v>133</v>
       </c>
     </row>
     <row r="65" spans="1:4">
       <c r="A65" t="s">
-        <v>133</v>
+        <v>103</v>
       </c>
       <c r="B65">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C65" t="s">
-        <v>168</v>
+        <v>131</v>
       </c>
       <c r="D65" t="s">
-        <v>181</v>
+        <v>137</v>
       </c>
     </row>
     <row r="66" spans="1:4">
       <c r="A66" t="s">
-        <v>22</v>
+        <v>104</v>
       </c>
       <c r="B66">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C66" t="s">
-        <v>165</v>
+        <v>133</v>
       </c>
       <c r="D66" t="s">
-        <v>174</v>
+        <v>134</v>
       </c>
     </row>
     <row r="67" spans="1:4">
       <c r="A67" t="s">
-        <v>134</v>
+        <v>105</v>
       </c>
       <c r="B67">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C67" t="s">
-        <v>165</v>
+        <v>133</v>
       </c>
       <c r="D67" t="s">
-        <v>178</v>
+        <v>137</v>
       </c>
     </row>
     <row r="68" spans="1:4">
       <c r="A68" t="s">
-        <v>17</v>
+        <v>106</v>
       </c>
       <c r="B68">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C68" t="s">
-        <v>168</v>
+        <v>137</v>
       </c>
       <c r="D68" t="s">
-        <v>180</v>
+        <v>135</v>
       </c>
     </row>
     <row r="69" spans="1:4">
       <c r="A69" t="s">
+        <v>107</v>
+      </c>
+      <c r="B69">
+        <v>2</v>
+      </c>
+      <c r="C69" t="s">
         <v>135</v>
       </c>
-      <c r="B69">
-        <v>4</v>
-      </c>
-      <c r="C69" t="s">
-        <v>172</v>
-      </c>
       <c r="D69" t="s">
-        <v>173</v>
+        <v>139</v>
       </c>
     </row>
     <row r="70" spans="1:4">
       <c r="A70" t="s">
-        <v>37</v>
+        <v>108</v>
       </c>
       <c r="B70">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C70" t="s">
-        <v>168</v>
+        <v>134</v>
       </c>
       <c r="D70" t="s">
-        <v>173</v>
+        <v>139</v>
       </c>
     </row>
     <row r="71" spans="1:4">
       <c r="A71" t="s">
-        <v>136</v>
+        <v>109</v>
       </c>
       <c r="B71">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C71" t="s">
-        <v>168</v>
+        <v>134</v>
       </c>
       <c r="D71" t="s">
-        <v>180</v>
+        <v>139</v>
       </c>
     </row>
     <row r="72" spans="1:4">
       <c r="A72" t="s">
-        <v>33</v>
+        <v>110</v>
       </c>
       <c r="B72">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C72" t="s">
-        <v>174</v>
+        <v>134</v>
       </c>
       <c r="D72" t="s">
-        <v>179</v>
+        <v>139</v>
       </c>
     </row>
     <row r="73" spans="1:4">
       <c r="A73" t="s">
-        <v>47</v>
+        <v>111</v>
       </c>
       <c r="B73">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C73" t="s">
-        <v>176</v>
+        <v>134</v>
       </c>
       <c r="D73" t="s">
-        <v>180</v>
+        <v>138</v>
       </c>
     </row>
     <row r="74" spans="1:4">
       <c r="A74" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="B74">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C74" t="s">
-        <v>167</v>
+        <v>138</v>
       </c>
       <c r="D74" t="s">
-        <v>178</v>
+        <v>139</v>
       </c>
     </row>
     <row r="75" spans="1:4">
       <c r="A75" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="B75">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C75" t="s">
-        <v>167</v>
+        <v>138</v>
       </c>
       <c r="D75" t="s">
-        <v>173</v>
+        <v>139</v>
       </c>
     </row>
     <row r="76" spans="1:4">
       <c r="A76" t="s">
-        <v>137</v>
+        <v>29</v>
       </c>
       <c r="B76">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C76" t="s">
-        <v>171</v>
+        <v>136</v>
       </c>
       <c r="D76" t="s">
-        <v>178</v>
+        <v>133</v>
       </c>
     </row>
     <row r="77" spans="1:4">
       <c r="A77" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="B77">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C77" t="s">
-        <v>171</v>
+        <v>138</v>
       </c>
       <c r="D77" t="s">
-        <v>179</v>
+        <v>139</v>
       </c>
     </row>
     <row r="78" spans="1:4">
       <c r="A78" t="s">
-        <v>31</v>
+        <v>112</v>
       </c>
       <c r="B78">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C78" t="s">
-        <v>174</v>
+        <v>138</v>
       </c>
       <c r="D78" t="s">
-        <v>179</v>
+        <v>140</v>
       </c>
     </row>
     <row r="79" spans="1:4">
       <c r="A79" t="s">
-        <v>48</v>
+        <v>113</v>
       </c>
       <c r="B79">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C79" t="s">
-        <v>171</v>
+        <v>134</v>
       </c>
       <c r="D79" t="s">
-        <v>180</v>
+        <v>134</v>
       </c>
     </row>
     <row r="80" spans="1:4">
       <c r="A80" t="s">
-        <v>138</v>
+        <v>114</v>
       </c>
       <c r="B80">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C80" t="s">
-        <v>166</v>
+        <v>134</v>
       </c>
       <c r="D80" t="s">
-        <v>177</v>
+        <v>134</v>
       </c>
     </row>
     <row r="81" spans="1:4">
       <c r="A81" t="s">
-        <v>139</v>
+        <v>115</v>
       </c>
       <c r="B81">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C81" t="s">
-        <v>177</v>
+        <v>135</v>
       </c>
       <c r="D81" t="s">
-        <v>183</v>
+        <v>135</v>
       </c>
     </row>
     <row r="82" spans="1:4">
       <c r="A82" t="s">
-        <v>140</v>
+        <v>116</v>
       </c>
       <c r="B82">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C82" t="s">
-        <v>168</v>
+        <v>138</v>
       </c>
       <c r="D82" t="s">
-        <v>175</v>
+        <v>138</v>
       </c>
     </row>
     <row r="83" spans="1:4">
       <c r="A83" t="s">
-        <v>141</v>
+        <v>117</v>
       </c>
       <c r="B83">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C83" t="s">
-        <v>168</v>
+        <v>135</v>
       </c>
       <c r="D83" t="s">
-        <v>174</v>
+        <v>135</v>
       </c>
     </row>
     <row r="84" spans="1:4">
       <c r="A84" t="s">
-        <v>142</v>
+        <v>118</v>
       </c>
       <c r="B84">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C84" t="s">
-        <v>165</v>
+        <v>135</v>
       </c>
       <c r="D84" t="s">
-        <v>171</v>
+        <v>135</v>
       </c>
     </row>
     <row r="85" spans="1:4">
       <c r="A85" t="s">
-        <v>143</v>
+        <v>119</v>
       </c>
       <c r="B85">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C85" t="s">
-        <v>166</v>
+        <v>138</v>
       </c>
       <c r="D85" t="s">
-        <v>167</v>
+        <v>138</v>
       </c>
     </row>
     <row r="86" spans="1:4">
       <c r="A86" t="s">
-        <v>144</v>
+        <v>120</v>
       </c>
       <c r="B86">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C86" t="s">
-        <v>165</v>
+        <v>138</v>
       </c>
       <c r="D86" t="s">
-        <v>171</v>
+        <v>138</v>
       </c>
     </row>
     <row r="87" spans="1:4">
       <c r="A87" t="s">
-        <v>145</v>
+        <v>121</v>
       </c>
       <c r="B87">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C87" t="s">
-        <v>176</v>
+        <v>138</v>
       </c>
       <c r="D87" t="s">
-        <v>183</v>
+        <v>138</v>
       </c>
     </row>
     <row r="88" spans="1:4">
       <c r="A88" t="s">
-        <v>28</v>
+        <v>122</v>
       </c>
       <c r="B88">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C88" t="s">
-        <v>171</v>
+        <v>138</v>
       </c>
       <c r="D88" t="s">
-        <v>174</v>
+        <v>138</v>
       </c>
     </row>
     <row r="89" spans="1:4">
       <c r="A89" t="s">
-        <v>146</v>
+        <v>123</v>
       </c>
       <c r="B89">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C89" t="s">
-        <v>167</v>
+        <v>138</v>
       </c>
       <c r="D89" t="s">
-        <v>175</v>
+        <v>138</v>
       </c>
     </row>
     <row r="90" spans="1:4">
       <c r="A90" t="s">
-        <v>19</v>
+        <v>124</v>
       </c>
       <c r="B90">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C90" t="s">
-        <v>168</v>
+        <v>138</v>
       </c>
       <c r="D90" t="s">
-        <v>172</v>
+        <v>138</v>
       </c>
     </row>
     <row r="91" spans="1:4">
       <c r="A91" t="s">
-        <v>147</v>
+        <v>125</v>
       </c>
       <c r="B91">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C91" t="s">
-        <v>172</v>
+        <v>139</v>
       </c>
       <c r="D91" t="s">
-        <v>176</v>
+        <v>139</v>
       </c>
     </row>
     <row r="92" spans="1:4">
       <c r="A92" t="s">
-        <v>148</v>
+        <v>126</v>
       </c>
       <c r="B92">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C92" t="s">
-        <v>171</v>
+        <v>140</v>
       </c>
       <c r="D92" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="93" spans="1:4">
-      <c r="A93" t="s">
-        <v>26</v>
-      </c>
-      <c r="B93">
-        <v>2</v>
-      </c>
-      <c r="C93" t="s">
-        <v>171</v>
-      </c>
-      <c r="D93" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="94" spans="1:4">
-      <c r="A94" t="s">
-        <v>149</v>
-      </c>
-      <c r="B94">
-        <v>2</v>
-      </c>
-      <c r="C94" t="s">
-        <v>175</v>
-      </c>
-      <c r="D94" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="95" spans="1:4">
-      <c r="A95" t="s">
-        <v>150</v>
-      </c>
-      <c r="B95">
-        <v>2</v>
-      </c>
-      <c r="C95" t="s">
-        <v>175</v>
-      </c>
-      <c r="D95" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="96" spans="1:4">
-      <c r="A96" t="s">
-        <v>44</v>
-      </c>
-      <c r="B96">
-        <v>2</v>
-      </c>
-      <c r="C96" t="s">
-        <v>175</v>
-      </c>
-      <c r="D96" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="97" spans="1:4">
-      <c r="A97" t="s">
-        <v>42</v>
-      </c>
-      <c r="B97">
-        <v>2</v>
-      </c>
-      <c r="C97" t="s">
-        <v>175</v>
-      </c>
-      <c r="D97" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="98" spans="1:4">
-      <c r="A98" t="s">
-        <v>151</v>
-      </c>
-      <c r="B98">
-        <v>2</v>
-      </c>
-      <c r="C98" t="s">
-        <v>173</v>
-      </c>
-      <c r="D98" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="99" spans="1:4">
-      <c r="A99" t="s">
-        <v>152</v>
-      </c>
-      <c r="B99">
-        <v>2</v>
-      </c>
-      <c r="C99" t="s">
-        <v>173</v>
-      </c>
-      <c r="D99" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="100" spans="1:4">
-      <c r="A100" t="s">
-        <v>153</v>
-      </c>
-      <c r="B100">
-        <v>2</v>
-      </c>
-      <c r="C100" t="s">
-        <v>173</v>
-      </c>
-      <c r="D100" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="101" spans="1:4">
-      <c r="A101" t="s">
-        <v>154</v>
-      </c>
-      <c r="B101">
-        <v>2</v>
-      </c>
-      <c r="C101" t="s">
-        <v>173</v>
-      </c>
-      <c r="D101" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="102" spans="1:4">
-      <c r="A102" t="s">
-        <v>155</v>
-      </c>
-      <c r="B102">
-        <v>2</v>
-      </c>
-      <c r="C102" t="s">
-        <v>173</v>
-      </c>
-      <c r="D102" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="103" spans="1:4">
-      <c r="A103" t="s">
-        <v>156</v>
-      </c>
-      <c r="B103">
-        <v>2</v>
-      </c>
-      <c r="C103" t="s">
-        <v>173</v>
-      </c>
-      <c r="D103" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="104" spans="1:4">
-      <c r="A104" t="s">
-        <v>157</v>
-      </c>
-      <c r="B104">
-        <v>2</v>
-      </c>
-      <c r="C104" t="s">
-        <v>173</v>
-      </c>
-      <c r="D104" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="105" spans="1:4">
-      <c r="A105" t="s">
-        <v>158</v>
-      </c>
-      <c r="B105">
-        <v>2</v>
-      </c>
-      <c r="C105" t="s">
-        <v>173</v>
-      </c>
-      <c r="D105" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="106" spans="1:4">
-      <c r="A106" t="s">
-        <v>159</v>
-      </c>
-      <c r="B106">
-        <v>2</v>
-      </c>
-      <c r="C106" t="s">
-        <v>178</v>
-      </c>
-      <c r="D106" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="107" spans="1:4">
-      <c r="A107" t="s">
-        <v>160</v>
-      </c>
-      <c r="B107">
-        <v>2</v>
-      </c>
-      <c r="C107" t="s">
-        <v>178</v>
-      </c>
-      <c r="D107" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="108" spans="1:4">
-      <c r="A108" t="s">
-        <v>161</v>
-      </c>
-      <c r="B108">
-        <v>2</v>
-      </c>
-      <c r="C108" t="s">
-        <v>179</v>
-      </c>
-      <c r="D108" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="109" spans="1:4">
-      <c r="A109" t="s">
-        <v>50</v>
-      </c>
-      <c r="B109">
-        <v>2</v>
-      </c>
-      <c r="C109" t="s">
-        <v>179</v>
-      </c>
-      <c r="D109" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="110" spans="1:4">
-      <c r="A110" t="s">
-        <v>46</v>
-      </c>
-      <c r="B110">
-        <v>2</v>
-      </c>
-      <c r="C110" t="s">
-        <v>179</v>
-      </c>
-      <c r="D110" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="111" spans="1:4">
-      <c r="A111" t="s">
-        <v>51</v>
-      </c>
-      <c r="B111">
-        <v>2</v>
-      </c>
-      <c r="C111" t="s">
-        <v>180</v>
-      </c>
-      <c r="D111" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="112" spans="1:4">
-      <c r="A112" t="s">
-        <v>52</v>
-      </c>
-      <c r="B112">
-        <v>2</v>
-      </c>
-      <c r="C112" t="s">
-        <v>180</v>
-      </c>
-      <c r="D112" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="113" spans="1:4">
-      <c r="A113" t="s">
-        <v>53</v>
-      </c>
-      <c r="B113">
-        <v>2</v>
-      </c>
-      <c r="C113" t="s">
-        <v>181</v>
-      </c>
-      <c r="D113" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="114" spans="1:4">
-      <c r="A114" t="s">
-        <v>54</v>
-      </c>
-      <c r="B114">
-        <v>2</v>
-      </c>
-      <c r="C114" t="s">
-        <v>181</v>
-      </c>
-      <c r="D114" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="115" spans="1:4">
-      <c r="A115" t="s">
-        <v>55</v>
-      </c>
-      <c r="B115">
-        <v>2</v>
-      </c>
-      <c r="C115" t="s">
-        <v>181</v>
-      </c>
-      <c r="D115" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="116" spans="1:4">
-      <c r="A116" t="s">
-        <v>162</v>
-      </c>
-      <c r="B116">
-        <v>2</v>
-      </c>
-      <c r="C116" t="s">
-        <v>181</v>
-      </c>
-      <c r="D116" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="117" spans="1:4">
-      <c r="A117" t="s">
-        <v>163</v>
-      </c>
-      <c r="B117">
-        <v>2</v>
-      </c>
-      <c r="C117" t="s">
-        <v>181</v>
-      </c>
-      <c r="D117" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="118" spans="1:4">
-      <c r="A118" t="s">
-        <v>57</v>
-      </c>
-      <c r="B118">
-        <v>2</v>
-      </c>
-      <c r="C118" t="s">
-        <v>182</v>
-      </c>
-      <c r="D118" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="119" spans="1:4">
-      <c r="A119" t="s">
-        <v>56</v>
-      </c>
-      <c r="B119">
-        <v>2</v>
-      </c>
-      <c r="C119" t="s">
-        <v>182</v>
-      </c>
-      <c r="D119" t="s">
-        <v>188</v>
+        <v>140</v>
       </c>
     </row>
   </sheetData>
